--- a/surgical_staging/STAGED_MMS200MI_Item_Master.xlsx
+++ b/surgical_staging/STAGED_MMS200MI_Item_Master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="251">
   <si>
     <t>MMCONO</t>
   </si>
@@ -232,6 +232,102 @@
     <t>MMCHID</t>
   </si>
   <si>
+    <t>MP_MMCONO</t>
+  </si>
+  <si>
+    <t>MP_MMITNO</t>
+  </si>
+  <si>
+    <t>MMSUNO</t>
+  </si>
+  <si>
+    <t>MMPUPR</t>
+  </si>
+  <si>
+    <t>MMPUCD</t>
+  </si>
+  <si>
+    <t>MMCUCD</t>
+  </si>
+  <si>
+    <t>MMPPDT</t>
+  </si>
+  <si>
+    <t>MMSAPR</t>
+  </si>
+  <si>
+    <t>MMSTUN</t>
+  </si>
+  <si>
+    <t>MMSACD</t>
+  </si>
+  <si>
+    <t>MMCUCS</t>
+  </si>
+  <si>
+    <t>MMSPDT</t>
+  </si>
+  <si>
+    <t>MMDIGI</t>
+  </si>
+  <si>
+    <t>MMBGRP</t>
+  </si>
+  <si>
+    <t>MMPRVG</t>
+  </si>
+  <si>
+    <t>MMFRE3</t>
+  </si>
+  <si>
+    <t>MMFRE4</t>
+  </si>
+  <si>
+    <t>MMEACD</t>
+  </si>
+  <si>
+    <t>MMOTDI</t>
+  </si>
+  <si>
+    <t>MMBOGR</t>
+  </si>
+  <si>
+    <t>MMPRGR</t>
+  </si>
+  <si>
+    <t>MMLAMA</t>
+  </si>
+  <si>
+    <t>MMACHK</t>
+  </si>
+  <si>
+    <t>MMBPEY</t>
+  </si>
+  <si>
+    <t>MMSPUN</t>
+  </si>
+  <si>
+    <t>MMSPUC</t>
+  </si>
+  <si>
+    <t>MMALUN</t>
+  </si>
+  <si>
+    <t>MP_MMRGDT</t>
+  </si>
+  <si>
+    <t>MP_MMRGTM</t>
+  </si>
+  <si>
+    <t>MP_MMLMDT</t>
+  </si>
+  <si>
+    <t>MP_MMCHNO</t>
+  </si>
+  <si>
+    <t>MP_MMCHID</t>
+  </si>
+  <si>
     <t>M9CONO</t>
   </si>
   <si>
@@ -448,37 +544,112 @@
     <t>M9CHID</t>
   </si>
   <si>
+    <t>M9SUNO</t>
+  </si>
+  <si>
+    <t>M9PUPR</t>
+  </si>
+  <si>
+    <t>M9PUCD</t>
+  </si>
+  <si>
+    <t>M9CUCD</t>
+  </si>
+  <si>
+    <t>M9PPDT</t>
+  </si>
+  <si>
+    <t>M9SAPR</t>
+  </si>
+  <si>
+    <t>M9STUN</t>
+  </si>
+  <si>
+    <t>M9SACD</t>
+  </si>
+  <si>
+    <t>M9CUCS</t>
+  </si>
+  <si>
+    <t>M9SPDT</t>
+  </si>
+  <si>
+    <t>M9DIGI</t>
+  </si>
+  <si>
+    <t>M9BGRP</t>
+  </si>
+  <si>
+    <t>M9PRVG</t>
+  </si>
+  <si>
+    <t>M9FRE3</t>
+  </si>
+  <si>
+    <t>M9FRE4</t>
+  </si>
+  <si>
+    <t>M9EACD</t>
+  </si>
+  <si>
+    <t>M9OTDI</t>
+  </si>
+  <si>
+    <t>M9BOGR</t>
+  </si>
+  <si>
+    <t>M9PRGR</t>
+  </si>
+  <si>
+    <t>M9LAMA</t>
+  </si>
+  <si>
+    <t>M9ACHK</t>
+  </si>
+  <si>
+    <t>M9BPEY</t>
+  </si>
+  <si>
+    <t>M9SPUN</t>
+  </si>
+  <si>
+    <t>M9SPUC</t>
+  </si>
+  <si>
+    <t>M9ALUN</t>
+  </si>
+  <si>
     <t>100.0</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t xml:space="preserve">AUT088013-0875 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS11017L       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS20537L       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T*ESC2 12 N / 875 N           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AT4403B/SOARUS/EVOH           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampacet 612413  Blue/White    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T*ESC2 12 N / 875 N                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEN 1.14 /  MI 3.5  / FDA  (shelf life: 360)                </t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                            </t>
+    <t xml:space="preserve">PK01D-OTB18    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PK01D-OTB18I   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PK01D-OTB18C   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTN UNP/OTB18                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTN UNP/OTB18 Inserts         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTN UNPTD/OTBC                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 5/8"  x  13 5/8"  x  3 3/8"                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTB Inserts - 2/case                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 5/8"  x  13 5/8"  x  3 1/2"   Cover                      </t>
   </si>
   <si>
     <t xml:space="preserve">                    </t>
@@ -487,64 +658,37 @@
     <t xml:space="preserve">W15PDA1   </t>
   </si>
   <si>
-    <t xml:space="preserve">W20       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W45MEDAM  </t>
+    <t xml:space="preserve">W41MECED  </t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t xml:space="preserve">M  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KG </t>
-  </si>
-  <si>
-    <t xml:space="preserve">850     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">800     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">810     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">342  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">300  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">301  </t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>P00</t>
-  </si>
-  <si>
-    <t>999</t>
+    <t xml:space="preserve">EA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">870     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">351  </t>
+  </si>
+  <si>
+    <t>910</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>RM</t>
+    <t>PK</t>
   </si>
   <si>
     <t>2.0</t>
   </si>
   <si>
-    <t>3.0</t>
-  </si>
-  <si>
     <t>1.0</t>
   </si>
   <si>
-    <t>1000.0</t>
+    <t xml:space="preserve">K  </t>
   </si>
   <si>
     <t xml:space="preserve">          </t>
@@ -562,15 +706,6 @@
     <t xml:space="preserve">    </t>
   </si>
   <si>
-    <t xml:space="preserve">N/A </t>
-  </si>
-  <si>
-    <t>384739.0</t>
-  </si>
-  <si>
-    <t>58060.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
@@ -583,12 +718,6 @@
     <t xml:space="preserve">*       </t>
   </si>
   <si>
-    <t xml:space="preserve">P285    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">        </t>
-  </si>
-  <si>
     <t>4.0</t>
   </si>
   <si>
@@ -598,52 +727,46 @@
     <t xml:space="preserve">N/A  </t>
   </si>
   <si>
-    <t>DIR</t>
-  </si>
-  <si>
     <t>000</t>
   </si>
   <si>
-    <t>20250611.0</t>
-  </si>
-  <si>
-    <t>20051025.0</t>
-  </si>
-  <si>
-    <t>20080115.0</t>
-  </si>
-  <si>
-    <t>151739.0</t>
-  </si>
-  <si>
-    <t>123820.0</t>
-  </si>
-  <si>
-    <t>102526.0</t>
-  </si>
-  <si>
-    <t>20200117.0</t>
-  </si>
-  <si>
-    <t>20210930.0</t>
-  </si>
-  <si>
-    <t>60.0</t>
-  </si>
-  <si>
-    <t>161.0</t>
-  </si>
-  <si>
-    <t>136.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W70MEICH  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W20PUROC  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W45MKCET  </t>
+    <t>20100303.0</t>
+  </si>
+  <si>
+    <t>20260401.0</t>
+  </si>
+  <si>
+    <t>20260306.0</t>
+  </si>
+  <si>
+    <t>144938.0</t>
+  </si>
+  <si>
+    <t>135203.0</t>
+  </si>
+  <si>
+    <t>113750.0</t>
+  </si>
+  <si>
+    <t>20260326.0</t>
+  </si>
+  <si>
+    <t>102.0</t>
+  </si>
+  <si>
+    <t>110.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W40MEBYS  </t>
+  </si>
+  <si>
+    <t>20260324.0</t>
+  </si>
+  <si>
+    <t>145149.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W15PCEHC  </t>
   </si>
 </sst>
 </file>
@@ -1001,10 +1124,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EN4"/>
+  <dimension ref="A1:GS4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:144">
+    <row r="1" spans="1:201">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1437,1307 +1560,1649 @@
       <c r="EN1" s="1" t="s">
         <v>143</v>
       </c>
+      <c r="EO1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="EP1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="EQ1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="ER1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="ES1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="ET1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="EU1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="EV1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="EW1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="EX1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="EY1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="EZ1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="FA1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="FB1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="FC1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="FD1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="FE1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="FF1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="FG1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="FH1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="FI1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="FJ1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="FK1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="FL1" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="FM1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="FN1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="FO1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="FP1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="FQ1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="FR1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="FS1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="FT1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="FU1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="FV1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="FW1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="FX1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="FY1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="FZ1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="GA1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="GB1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="GC1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="GD1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="GE1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="GF1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="GG1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="GH1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="GI1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="GJ1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="GK1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="GL1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="GM1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="GN1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="GO1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="GP1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="GQ1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="GR1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="GS1" s="1" t="s">
+        <v>200</v>
+      </c>
     </row>
-    <row r="2" spans="1:144">
+    <row r="2" spans="1:201">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>209</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="G2" t="s">
-        <v>156</v>
+        <v>213</v>
       </c>
       <c r="H2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="I2" t="s">
-        <v>160</v>
+        <v>216</v>
       </c>
       <c r="J2" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="K2" t="s">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="L2" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="M2" t="s">
-        <v>171</v>
+        <v>220</v>
       </c>
       <c r="N2" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="O2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="P2" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="Q2" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="R2" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="S2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="T2" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="U2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="V2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="W2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="X2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="Y2" t="s">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="Z2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AA2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AB2" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="AC2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AD2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AE2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AF2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AG2" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="AH2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AI2" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="AJ2" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="AK2" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="AL2" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="AM2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AN2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="AO2" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="AP2" t="s">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="AQ2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AR2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AS2" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="AT2" t="s">
-        <v>187</v>
+        <v>232</v>
       </c>
       <c r="AU2" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="AV2" t="s">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="AW2" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="AX2" t="s">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="AY2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="AZ2" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="BA2" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="BB2" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="BC2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="BD2" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="BE2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="BF2" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="BG2" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="BH2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="BI2" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="BJ2" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="BK2" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="BL2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="BM2" t="s">
-        <v>159</v>
+        <v>223</v>
       </c>
       <c r="BN2" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="BO2" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="BP2" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="BQ2" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="BR2" t="s">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="BS2" t="s">
+        <v>245</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>214</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>201</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>203</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>225</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>215</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>226</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>215</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>215</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>216</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>215</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>226</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>215</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>230</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>230</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>230</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>227</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>227</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>215</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>223</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>222</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>222</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>215</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>215</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>215</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>216</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>223</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>216</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>248</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>249</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>248</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>222</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>250</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>202</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>206</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>209</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>212</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>213</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>215</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>216</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>217</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>218</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>220</v>
+      </c>
+      <c r="DN2" t="s">
+        <v>221</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>215</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>222</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>215</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>223</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>215</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>223</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>215</v>
+      </c>
+      <c r="DV2" t="s">
+        <v>215</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>215</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>215</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>224</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>215</v>
+      </c>
+      <c r="ED2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EE2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EF2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EG2" t="s">
+        <v>225</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>226</v>
+      </c>
+      <c r="EJ2" t="s">
+        <v>227</v>
+      </c>
+      <c r="EK2" t="s">
+        <v>228</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>229</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EO2" t="s">
+        <v>229</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>230</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>215</v>
+      </c>
+      <c r="ER2" t="s">
+        <v>215</v>
+      </c>
+      <c r="ES2" t="s">
+        <v>231</v>
+      </c>
+      <c r="ET2" t="s">
+        <v>232</v>
+      </c>
+      <c r="EU2" t="s">
+        <v>226</v>
+      </c>
+      <c r="EV2" t="s">
+        <v>233</v>
+      </c>
+      <c r="EW2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EX2" t="s">
+        <v>224</v>
+      </c>
+      <c r="EY2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EZ2" t="s">
+        <v>222</v>
+      </c>
+      <c r="FA2" t="s">
+        <v>234</v>
+      </c>
+      <c r="FB2" t="s">
+        <v>234</v>
+      </c>
+      <c r="FC2" t="s">
+        <v>215</v>
+      </c>
+      <c r="FD2" t="s">
+        <v>225</v>
+      </c>
+      <c r="FE2" t="s">
+        <v>215</v>
+      </c>
+      <c r="FF2" t="s">
+        <v>235</v>
+      </c>
+      <c r="FG2" t="s">
+        <v>236</v>
+      </c>
+      <c r="FH2" t="s">
+        <v>215</v>
+      </c>
+      <c r="FI2" t="s">
+        <v>226</v>
+      </c>
+      <c r="FJ2" t="s">
+        <v>231</v>
+      </c>
+      <c r="FK2" t="s">
+        <v>226</v>
+      </c>
+      <c r="FL2" t="s">
+        <v>215</v>
+      </c>
+      <c r="FM2" t="s">
+        <v>223</v>
+      </c>
+      <c r="FN2" t="s">
+        <v>215</v>
+      </c>
+      <c r="FO2" t="s">
+        <v>226</v>
+      </c>
+      <c r="FP2" t="s">
+        <v>238</v>
+      </c>
+      <c r="FQ2" t="s">
+        <v>241</v>
+      </c>
+      <c r="FR2" t="s">
+        <v>244</v>
+      </c>
+      <c r="FS2" t="s">
+        <v>245</v>
+      </c>
+      <c r="FT2" t="s">
+        <v>214</v>
+      </c>
+      <c r="FU2" t="s">
+        <v>225</v>
+      </c>
+      <c r="FV2" t="s">
+        <v>215</v>
+      </c>
+      <c r="FW2" t="s">
+        <v>215</v>
+      </c>
+      <c r="FX2" t="s">
+        <v>226</v>
+      </c>
+      <c r="FY2" t="s">
+        <v>215</v>
+      </c>
+      <c r="FZ2" t="s">
+        <v>215</v>
+      </c>
+      <c r="GA2" t="s">
+        <v>216</v>
+      </c>
+      <c r="GB2" t="s">
+        <v>215</v>
+      </c>
+      <c r="GC2" t="s">
+        <v>226</v>
+      </c>
+      <c r="GD2" t="s">
+        <v>215</v>
+      </c>
+      <c r="GE2" t="s">
+        <v>230</v>
+      </c>
+      <c r="GF2" t="s">
+        <v>230</v>
+      </c>
+      <c r="GG2" t="s">
+        <v>230</v>
+      </c>
+      <c r="GH2" t="s">
+        <v>227</v>
+      </c>
+      <c r="GI2" t="s">
+        <v>227</v>
+      </c>
+      <c r="GJ2" t="s">
+        <v>215</v>
+      </c>
+      <c r="GK2" t="s">
+        <v>223</v>
+      </c>
+      <c r="GL2" t="s">
+        <v>222</v>
+      </c>
+      <c r="GM2" t="s">
+        <v>222</v>
+      </c>
+      <c r="GN2" t="s">
+        <v>215</v>
+      </c>
+      <c r="GO2" t="s">
+        <v>215</v>
+      </c>
+      <c r="GP2" t="s">
+        <v>215</v>
+      </c>
+      <c r="GQ2" t="s">
+        <v>216</v>
+      </c>
+      <c r="GR2" t="s">
+        <v>223</v>
+      </c>
+      <c r="GS2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:201">
+      <c r="A3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" t="s">
         <v>204</v>
       </c>
-      <c r="BT2" t="s">
+      <c r="D3" t="s">
         <v>207</v>
       </c>
-      <c r="BU2" t="s">
-        <v>144</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BW2" t="s">
-        <v>146</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>155</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>156</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>160</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>162</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>165</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>168</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>171</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>172</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>173</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>174</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>175</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>175</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>161</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>176</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>159</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>159</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>177</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>159</v>
-      </c>
-      <c r="DC2" t="s">
-        <v>178</v>
-      </c>
-      <c r="DD2" t="s">
-        <v>179</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>180</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>181</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>159</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>181</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DK2" t="s">
-        <v>159</v>
-      </c>
-      <c r="DL2" t="s">
-        <v>159</v>
-      </c>
-      <c r="DM2" t="s">
-        <v>186</v>
-      </c>
-      <c r="DN2" t="s">
-        <v>187</v>
-      </c>
-      <c r="DO2" t="s">
-        <v>178</v>
-      </c>
-      <c r="DP2" t="s">
-        <v>188</v>
-      </c>
-      <c r="DQ2" t="s">
-        <v>174</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>161</v>
-      </c>
-      <c r="DS2" t="s">
-        <v>159</v>
-      </c>
-      <c r="DT2" t="s">
-        <v>173</v>
-      </c>
-      <c r="DU2" t="s">
-        <v>191</v>
-      </c>
-      <c r="DV2" t="s">
-        <v>191</v>
-      </c>
-      <c r="DW2" t="s">
-        <v>159</v>
-      </c>
-      <c r="DX2" t="s">
-        <v>177</v>
-      </c>
-      <c r="DY2" t="s">
-        <v>159</v>
-      </c>
-      <c r="DZ2" t="s">
-        <v>192</v>
-      </c>
-      <c r="EA2" t="s">
-        <v>193</v>
-      </c>
-      <c r="EB2" t="s">
-        <v>159</v>
-      </c>
-      <c r="EC2" t="s">
-        <v>178</v>
-      </c>
-      <c r="ED2" t="s">
-        <v>186</v>
-      </c>
-      <c r="EE2" t="s">
-        <v>178</v>
-      </c>
-      <c r="EF2" t="s">
-        <v>159</v>
-      </c>
-      <c r="EG2" t="s">
-        <v>159</v>
-      </c>
-      <c r="EH2" t="s">
-        <v>159</v>
-      </c>
-      <c r="EI2" t="s">
-        <v>178</v>
-      </c>
-      <c r="EJ2" t="s">
-        <v>196</v>
-      </c>
-      <c r="EK2" t="s">
-        <v>199</v>
-      </c>
-      <c r="EL2" t="s">
-        <v>196</v>
-      </c>
-      <c r="EM2" t="s">
+      <c r="E3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K3" t="s">
+        <v>218</v>
+      </c>
+      <c r="L3" t="s">
+        <v>219</v>
+      </c>
+      <c r="M3" t="s">
+        <v>220</v>
+      </c>
+      <c r="N3" t="s">
+        <v>221</v>
+      </c>
+      <c r="O3" t="s">
+        <v>215</v>
+      </c>
+      <c r="P3" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>215</v>
+      </c>
+      <c r="R3" t="s">
+        <v>223</v>
+      </c>
+      <c r="S3" t="s">
+        <v>215</v>
+      </c>
+      <c r="T3" t="s">
+        <v>223</v>
+      </c>
+      <c r="U3" t="s">
+        <v>215</v>
+      </c>
+      <c r="V3" t="s">
+        <v>215</v>
+      </c>
+      <c r="W3" t="s">
+        <v>215</v>
+      </c>
+      <c r="X3" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>224</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>225</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>227</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>229</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>229</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>232</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>226</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>233</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>224</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>215</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>222</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>234</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>234</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>215</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>225</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>215</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>235</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>236</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>215</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>226</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>231</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>215</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>215</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>215</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>226</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>239</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>242</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>239</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>246</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>214</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>201</v>
+      </c>
+      <c r="DB3" t="s">
+        <v>202</v>
+      </c>
+      <c r="DC3" t="s">
         <v>204</v>
       </c>
-      <c r="EN2" t="s">
+      <c r="DD3" t="s">
         <v>207</v>
       </c>
+      <c r="DE3" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF3" t="s">
+        <v>212</v>
+      </c>
+      <c r="DG3" t="s">
+        <v>214</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>215</v>
+      </c>
+      <c r="DI3" t="s">
+        <v>216</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>217</v>
+      </c>
+      <c r="DK3" t="s">
+        <v>218</v>
+      </c>
+      <c r="DL3" t="s">
+        <v>219</v>
+      </c>
+      <c r="DM3" t="s">
+        <v>220</v>
+      </c>
+      <c r="DN3" t="s">
+        <v>221</v>
+      </c>
+      <c r="DO3" t="s">
+        <v>215</v>
+      </c>
+      <c r="DP3" t="s">
+        <v>222</v>
+      </c>
+      <c r="DQ3" t="s">
+        <v>215</v>
+      </c>
+      <c r="DR3" t="s">
+        <v>223</v>
+      </c>
+      <c r="DS3" t="s">
+        <v>215</v>
+      </c>
+      <c r="DT3" t="s">
+        <v>223</v>
+      </c>
+      <c r="DU3" t="s">
+        <v>215</v>
+      </c>
+      <c r="DV3" t="s">
+        <v>215</v>
+      </c>
+      <c r="DW3" t="s">
+        <v>215</v>
+      </c>
+      <c r="DX3" t="s">
+        <v>215</v>
+      </c>
+      <c r="DY3" t="s">
+        <v>224</v>
+      </c>
+      <c r="DZ3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EA3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EB3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EC3" t="s">
+        <v>215</v>
+      </c>
+      <c r="ED3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EE3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EF3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EG3" t="s">
+        <v>225</v>
+      </c>
+      <c r="EH3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EI3" t="s">
+        <v>226</v>
+      </c>
+      <c r="EJ3" t="s">
+        <v>227</v>
+      </c>
+      <c r="EK3" t="s">
+        <v>228</v>
+      </c>
+      <c r="EL3" t="s">
+        <v>229</v>
+      </c>
+      <c r="EM3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EO3" t="s">
+        <v>229</v>
+      </c>
+      <c r="EP3" t="s">
+        <v>230</v>
+      </c>
+      <c r="EQ3" t="s">
+        <v>215</v>
+      </c>
+      <c r="ER3" t="s">
+        <v>215</v>
+      </c>
+      <c r="ES3" t="s">
+        <v>231</v>
+      </c>
+      <c r="ET3" t="s">
+        <v>232</v>
+      </c>
+      <c r="EU3" t="s">
+        <v>226</v>
+      </c>
+      <c r="EV3" t="s">
+        <v>233</v>
+      </c>
+      <c r="EW3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EX3" t="s">
+        <v>224</v>
+      </c>
+      <c r="EY3" t="s">
+        <v>215</v>
+      </c>
+      <c r="EZ3" t="s">
+        <v>222</v>
+      </c>
+      <c r="FA3" t="s">
+        <v>234</v>
+      </c>
+      <c r="FB3" t="s">
+        <v>234</v>
+      </c>
+      <c r="FC3" t="s">
+        <v>215</v>
+      </c>
+      <c r="FD3" t="s">
+        <v>225</v>
+      </c>
+      <c r="FE3" t="s">
+        <v>215</v>
+      </c>
+      <c r="FF3" t="s">
+        <v>235</v>
+      </c>
+      <c r="FG3" t="s">
+        <v>236</v>
+      </c>
+      <c r="FH3" t="s">
+        <v>215</v>
+      </c>
+      <c r="FI3" t="s">
+        <v>226</v>
+      </c>
+      <c r="FJ3" t="s">
+        <v>231</v>
+      </c>
+      <c r="FK3" t="s">
+        <v>226</v>
+      </c>
+      <c r="FL3" t="s">
+        <v>215</v>
+      </c>
+      <c r="FM3" t="s">
+        <v>215</v>
+      </c>
+      <c r="FN3" t="s">
+        <v>215</v>
+      </c>
+      <c r="FO3" t="s">
+        <v>226</v>
+      </c>
+      <c r="FP3" t="s">
+        <v>239</v>
+      </c>
+      <c r="FQ3" t="s">
+        <v>242</v>
+      </c>
+      <c r="FR3" t="s">
+        <v>239</v>
+      </c>
+      <c r="FS3" t="s">
+        <v>246</v>
+      </c>
+      <c r="FT3" t="s">
+        <v>214</v>
+      </c>
     </row>
-    <row r="3" spans="1:144">
-      <c r="A3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J3" t="s">
-        <v>163</v>
-      </c>
-      <c r="K3" t="s">
-        <v>166</v>
-      </c>
-      <c r="L3" t="s">
-        <v>169</v>
-      </c>
-      <c r="M3" t="s">
-        <v>171</v>
-      </c>
-      <c r="N3" t="s">
-        <v>172</v>
-      </c>
-      <c r="O3" t="s">
-        <v>159</v>
-      </c>
-      <c r="P3" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>159</v>
-      </c>
-      <c r="R3" t="s">
-        <v>175</v>
-      </c>
-      <c r="S3" t="s">
-        <v>159</v>
-      </c>
-      <c r="T3" t="s">
-        <v>175</v>
-      </c>
-      <c r="U3" t="s">
-        <v>159</v>
-      </c>
-      <c r="V3" t="s">
-        <v>173</v>
-      </c>
-      <c r="W3" t="s">
-        <v>175</v>
-      </c>
-      <c r="X3" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>178</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>180</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>182</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>184</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>181</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>185</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>186</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>187</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>178</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>189</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>174</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>161</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>173</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>191</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>191</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>177</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>192</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>193</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>178</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>186</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>194</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>195</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>197</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>200</v>
-      </c>
-      <c r="BR3" t="s">
+    <row r="4" spans="1:201">
+      <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" t="s">
         <v>202</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="C4" t="s">
         <v>205</v>
       </c>
-      <c r="BT3" t="s">
+      <c r="D4" t="s">
         <v>208</v>
       </c>
-      <c r="BU3" t="s">
-        <v>144</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>145</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>147</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>153</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>155</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>157</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CC3" t="s">
-        <v>161</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>163</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>166</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>169</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>171</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>172</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>173</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>175</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>175</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>173</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>175</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>175</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>161</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>159</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>159</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>177</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>159</v>
-      </c>
-      <c r="DC3" t="s">
-        <v>178</v>
-      </c>
-      <c r="DD3" t="s">
-        <v>179</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>180</v>
-      </c>
-      <c r="DF3" t="s">
-        <v>182</v>
-      </c>
-      <c r="DG3" t="s">
-        <v>159</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>184</v>
-      </c>
-      <c r="DI3" t="s">
-        <v>181</v>
-      </c>
-      <c r="DJ3" t="s">
-        <v>185</v>
-      </c>
-      <c r="DK3" t="s">
-        <v>159</v>
-      </c>
-      <c r="DL3" t="s">
-        <v>159</v>
-      </c>
-      <c r="DM3" t="s">
-        <v>186</v>
-      </c>
-      <c r="DN3" t="s">
-        <v>187</v>
-      </c>
-      <c r="DO3" t="s">
-        <v>178</v>
-      </c>
-      <c r="DP3" t="s">
-        <v>189</v>
-      </c>
-      <c r="DQ3" t="s">
-        <v>174</v>
-      </c>
-      <c r="DR3" t="s">
-        <v>161</v>
-      </c>
-      <c r="DS3" t="s">
-        <v>159</v>
-      </c>
-      <c r="DT3" t="s">
-        <v>173</v>
-      </c>
-      <c r="DU3" t="s">
-        <v>191</v>
-      </c>
-      <c r="DV3" t="s">
-        <v>191</v>
-      </c>
-      <c r="DW3" t="s">
-        <v>159</v>
-      </c>
-      <c r="DX3" t="s">
-        <v>177</v>
-      </c>
-      <c r="DY3" t="s">
-        <v>159</v>
-      </c>
-      <c r="DZ3" t="s">
-        <v>192</v>
-      </c>
-      <c r="EA3" t="s">
-        <v>193</v>
-      </c>
-      <c r="EB3" t="s">
-        <v>159</v>
-      </c>
-      <c r="EC3" t="s">
-        <v>178</v>
-      </c>
-      <c r="ED3" t="s">
-        <v>186</v>
-      </c>
-      <c r="EE3" t="s">
-        <v>194</v>
-      </c>
-      <c r="EF3" t="s">
-        <v>159</v>
-      </c>
-      <c r="EG3" t="s">
-        <v>159</v>
-      </c>
-      <c r="EH3" t="s">
-        <v>159</v>
-      </c>
-      <c r="EI3" t="s">
-        <v>195</v>
-      </c>
-      <c r="EJ3" t="s">
-        <v>197</v>
-      </c>
-      <c r="EK3" t="s">
-        <v>200</v>
-      </c>
-      <c r="EL3" t="s">
+      <c r="E4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G4" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" t="s">
+        <v>216</v>
+      </c>
+      <c r="J4" t="s">
+        <v>217</v>
+      </c>
+      <c r="K4" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" t="s">
+        <v>219</v>
+      </c>
+      <c r="M4" t="s">
+        <v>220</v>
+      </c>
+      <c r="N4" t="s">
+        <v>221</v>
+      </c>
+      <c r="O4" t="s">
+        <v>215</v>
+      </c>
+      <c r="P4" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>215</v>
+      </c>
+      <c r="R4" t="s">
+        <v>223</v>
+      </c>
+      <c r="S4" t="s">
+        <v>215</v>
+      </c>
+      <c r="T4" t="s">
+        <v>223</v>
+      </c>
+      <c r="U4" t="s">
+        <v>215</v>
+      </c>
+      <c r="V4" t="s">
+        <v>215</v>
+      </c>
+      <c r="W4" t="s">
+        <v>215</v>
+      </c>
+      <c r="X4" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>224</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>225</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>227</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>229</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>229</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>230</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>232</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>226</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>233</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>222</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>234</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>234</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>215</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>225</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>215</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>235</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>236</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>215</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>226</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>231</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>226</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>215</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>215</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>215</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>237</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>240</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>243</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>240</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>245</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>247</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>201</v>
+      </c>
+      <c r="DB4" t="s">
         <v>202</v>
       </c>
-      <c r="EM3" t="s">
+      <c r="DC4" t="s">
         <v>205</v>
       </c>
-      <c r="EN3" t="s">
+      <c r="DD4" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="4" spans="1:144">
-      <c r="A4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" t="s">
-        <v>159</v>
-      </c>
-      <c r="I4" t="s">
-        <v>161</v>
-      </c>
-      <c r="J4" t="s">
-        <v>164</v>
-      </c>
-      <c r="K4" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" t="s">
-        <v>170</v>
-      </c>
-      <c r="M4" t="s">
-        <v>171</v>
-      </c>
-      <c r="N4" t="s">
-        <v>172</v>
-      </c>
-      <c r="O4" t="s">
-        <v>159</v>
-      </c>
-      <c r="P4" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>159</v>
-      </c>
-      <c r="R4" t="s">
-        <v>175</v>
-      </c>
-      <c r="S4" t="s">
-        <v>159</v>
-      </c>
-      <c r="T4" t="s">
-        <v>175</v>
-      </c>
-      <c r="U4" t="s">
-        <v>174</v>
-      </c>
-      <c r="V4" t="s">
-        <v>173</v>
-      </c>
-      <c r="W4" t="s">
-        <v>159</v>
-      </c>
-      <c r="X4" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>178</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>179</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>180</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>181</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>181</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>185</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>186</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>187</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>178</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>190</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>161</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>159</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>173</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>191</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>191</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>177</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>177</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>179</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>178</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>186</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>178</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>195</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>198</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>201</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>203</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>206</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>209</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>144</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>148</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>151</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>154</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>155</v>
-      </c>
-      <c r="CA4" t="s">
-        <v>158</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CC4" t="s">
-        <v>161</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>164</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>167</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>170</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>171</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>172</v>
-      </c>
-      <c r="CI4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CJ4" t="s">
-        <v>173</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>175</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>175</v>
-      </c>
-      <c r="CO4" t="s">
-        <v>174</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>173</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>161</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CU4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CV4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CW4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CX4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CY4" t="s">
-        <v>159</v>
-      </c>
-      <c r="CZ4" t="s">
-        <v>159</v>
-      </c>
-      <c r="DA4" t="s">
-        <v>177</v>
-      </c>
-      <c r="DB4" t="s">
-        <v>159</v>
-      </c>
-      <c r="DC4" t="s">
-        <v>178</v>
-      </c>
-      <c r="DD4" t="s">
-        <v>179</v>
-      </c>
       <c r="DE4" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="DF4" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="DG4" t="s">
-        <v>159</v>
+        <v>213</v>
       </c>
       <c r="DH4" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="DI4" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="DJ4" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="DK4" t="s">
-        <v>159</v>
+        <v>218</v>
       </c>
       <c r="DL4" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="DM4" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="DN4" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="DO4" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="DP4" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="DQ4" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="DR4" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="DS4" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="DT4" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="DU4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="DV4" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="DW4" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="DX4" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="DY4" t="s">
-        <v>159</v>
+        <v>224</v>
       </c>
       <c r="DZ4" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="EA4" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="EB4" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="EC4" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="ED4" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="EE4" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="EF4" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="EG4" t="s">
-        <v>159</v>
+        <v>225</v>
       </c>
       <c r="EH4" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="EI4" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="EJ4" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="EK4" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="EL4" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="EM4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="EN4" t="s">
-        <v>209</v>
+        <v>215</v>
+      </c>
+      <c r="EO4" t="s">
+        <v>229</v>
+      </c>
+      <c r="EP4" t="s">
+        <v>230</v>
+      </c>
+      <c r="EQ4" t="s">
+        <v>215</v>
+      </c>
+      <c r="ER4" t="s">
+        <v>215</v>
+      </c>
+      <c r="ES4" t="s">
+        <v>231</v>
+      </c>
+      <c r="ET4" t="s">
+        <v>232</v>
+      </c>
+      <c r="EU4" t="s">
+        <v>226</v>
+      </c>
+      <c r="EV4" t="s">
+        <v>233</v>
+      </c>
+      <c r="EW4" t="s">
+        <v>215</v>
+      </c>
+      <c r="EX4" t="s">
+        <v>224</v>
+      </c>
+      <c r="EY4" t="s">
+        <v>215</v>
+      </c>
+      <c r="EZ4" t="s">
+        <v>222</v>
+      </c>
+      <c r="FA4" t="s">
+        <v>234</v>
+      </c>
+      <c r="FB4" t="s">
+        <v>234</v>
+      </c>
+      <c r="FC4" t="s">
+        <v>215</v>
+      </c>
+      <c r="FD4" t="s">
+        <v>225</v>
+      </c>
+      <c r="FE4" t="s">
+        <v>215</v>
+      </c>
+      <c r="FF4" t="s">
+        <v>235</v>
+      </c>
+      <c r="FG4" t="s">
+        <v>236</v>
+      </c>
+      <c r="FH4" t="s">
+        <v>215</v>
+      </c>
+      <c r="FI4" t="s">
+        <v>226</v>
+      </c>
+      <c r="FJ4" t="s">
+        <v>231</v>
+      </c>
+      <c r="FK4" t="s">
+        <v>226</v>
+      </c>
+      <c r="FL4" t="s">
+        <v>215</v>
+      </c>
+      <c r="FM4" t="s">
+        <v>215</v>
+      </c>
+      <c r="FN4" t="s">
+        <v>215</v>
+      </c>
+      <c r="FO4" t="s">
+        <v>237</v>
+      </c>
+      <c r="FP4" t="s">
+        <v>240</v>
+      </c>
+      <c r="FQ4" t="s">
+        <v>243</v>
+      </c>
+      <c r="FR4" t="s">
+        <v>240</v>
+      </c>
+      <c r="FS4" t="s">
+        <v>245</v>
+      </c>
+      <c r="FT4" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
